--- a/stories/arbres/ATOM-JEU.REG.002-04.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Bérénice joue dans le jardin. Papa est là. Il y a des quilles en bois. Papa dit une règle. Une règle : on attend. Puis on fait rouler la balle. Bérénice écoute. Elle prend la balle trop vite. Papa va la rappeler une fois. Il dit : on attend. C'est la règle. Bérénice s'arrête. Elle attend. Puis elle fait rouler la balle. Une quille tombe. Bérénice sourit. Papa dit : tu as suivi la règle. Bérénice répète : on attend. Une règle simple. Papa la rappelle. Bérénice la suit. Plus tard, ils jouent au ballon souple. Papa dit une règle. Une règle : on se passe le ballon. Bérénice se souvient. Papa va la rappeler une fois. Bérénice attend. Puis elle passe le ballon. Même leçon, autre jeu. Une règle. On la rappelle. On la suit.</t>
+          <t>Bérénice joue dans le jardin. Papa est là. Il y a des quilles en bois. Papa dit une règle. Une règle : on attend. Puis on fait rouler la balle. Bérénice écoute. Elle prend la balle trop vite. Papa va la rappeler une fois. On attend. C'est la règle. Bérénice s'arrête. Elle attend. Puis elle fait rouler la balle. Une quille tombe. Bérénice sourit. Tu as suivi la règle. Bérénice répète : on attend. Une règle simple. Papa la rappelle. Bérénice la suit. Plus tard, ils jouent au ballon souple. Papa dit une règle. Une règle : on se passe le ballon. Bérénice se souvient. Papa va la rappeler une fois. Bérénice attend. Puis elle passe le ballon. Même leçon, autre jeu. Une règle. On la rappelle. On la suit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Bérénice joue dans le jardin. Papa est là. Il y a des quilles en bois. Papa dit une règle. Une règle : on attend. Puis on fait rouler la balle. Bérénice écoute. Elle prend la balle trop vite. Papa va la rappeler une fois.
+narrateur|On attend. C'est la règle.
+narrateur|Bérénice s'arrête. Elle attend. Puis elle fait rouler la balle. Une quille tombe. Bérénice sourit.
+papa|Tu as suivi la règle.
+narrateur|Bérénice répète : on attend. Une règle simple. Papa la rappelle. Bérénice la suit. Plus tard, ils jouent au ballon souple. Papa dit une règle. Une règle : on se passe le ballon. Bérénice se souvient. Papa va la rappeler une fois. Bérénice attend. Puis elle passe le ballon. Même leçon, autre jeu. Une règle. On la rappelle. On la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Bérénice joue. Que suit-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Bérénice a suivi la règle. Papa a su la rappeler. Plus tard, au ballon, pareil.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Bérénice pose la balle. Papa lui verse de l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-04.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Bérénice répète : on attend. Une règle simple. Papa la rappelle. Bérénice la suit. Plus tard, ils jouent au ballon souple. Papa dit une règle. Une règle : on se passe le ballon. Bérénice se souvient. Papa va la rappeler une fois. Bérénice attend. Puis elle passe le ballon. Même leçon, autre jeu. Une règle. On la rappelle. On la suit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Bérénice joue. Que suit-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Bérénice a suivi la règle. Papa a su la rappeler. Plus tard, au ballon, pareil.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Bérénice pose la balle. Papa lui verse de l'eau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.REG.002-04.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bérénice suit une règle, deux jeux</t>
+          <t>Les quilles de Chouchou, puis le ballon</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Au jardin, Chouchou suit une règle aux quilles, puis au ballon. Papa rappelle une fois, chaque fois.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Bérénice joue dans le jardin. Papa est là. Il y a des quilles en bois. Papa dit une règle. Une règle : on attend. Puis on fait rouler la balle. Bérénice écoute. Elle prend la balle trop vite. Papa va la rappeler une fois. On attend. C'est la règle. Bérénice s'arrête. Elle attend. Puis elle fait rouler la balle. Une quille tombe. Bérénice sourit. Tu as suivi la règle. Bérénice répète : on attend. Une règle simple. Papa la rappelle. Bérénice la suit. Plus tard, ils jouent au ballon souple. Papa dit une règle. Une règle : on se passe le ballon. Bérénice se souvient. Papa va la rappeler une fois. Bérénice attend. Puis elle passe le ballon. Même leçon, autre jeu. Une règle. On la rappelle. On la suit.</t>
+          <t>Une file de fourmis traverse l'allée. Les quilles en bois sentent le pin. Une balle ronde attend près du seau. L'herbe du jardin est un peu sèche. Un oiseau pique le sol, tout près. Le seau a un peu de terre au fond. Le bois des quilles est lisse et chaud. Une feuille colle à une quille. Un nuage passe. L'ombre bouge. Le seau sent un peu la terre. Une coccinelle marche sur une quille. Elle s'envole. La quille reste. Tu as vu les fourmis, Chouchou ? Oui, papa. Elles marchent en file. En ce moment, papa pose les quilles. Elles font un petit bruit sourd. Une règle. On attend. Puis on fait rouler la balle. J'ai envie de rouler. On attend. Je te la rappelle une fois. C'est la règle. Chouchou attend, la balle près du pied. Puis il fait rouler la balle. Une quille tombe. Le bois claque. Elle est tombée. Tu as suivi la règle. Tu as attendu. Bravo, Chouchou. On attend. Puis on roule. Oui. Une règle simple. On la rappelle. Plus tard, le soleil a un peu baissé. Papa sort un ballon souple. Le ballon sent le caoutchouc tiède. Une règle. On se passe le ballon. On attend. Puis on passe. Je me souviens. On attend. Oui. Je te la rappelle une fois. Chouchou attend. Puis il passe le ballon. Tu as suivi la règle dite. Au ballon, la même règle. Bravo. Une règle. On la rappelle. Oui. Tu la suis. Tu as fait du bon travail. Les fourmis sont encore dans l'allée. Les quilles reposent près du seau. Tu as attendu aux quilles, puis au ballon ? Oui. Deux jeux. Une règle. Bravo, Chouchou. On la rappelle. On la suit. Le ballon souple repose dans l'herbe. Tu as attendu, chaque fois ? Oui. Quilles, puis ballon. Une règle. Je la rappelle. Tu la suis. Les fourmis avancent encore. L'herbe pique un peu les chevilles.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Bérénice joue dans le jardin. Papa est là. Il y a des quilles en bois. Papa dit une règle. Une règle : on attend. Puis on fait rouler la balle. Bérénice écoute. Elle prend la balle trop vite. Papa va la rappeler une fois.
-narrateur|On attend. C'est la règle.
-narrateur|Bérénice s'arrête. Elle attend. Puis elle fait rouler la balle. Une quille tombe. Bérénice sourit.
+          <t>narrateur|Une file de fourmis traverse l'allée.
+narrateur|Les quilles en bois sentent le pin.
+narrateur|Une balle ronde attend près du seau.
+narrateur|L'herbe du jardin est un peu sèche.
+narrateur|Un oiseau pique le sol, tout près.
+narrateur|Le seau a un peu de terre au fond.
+narrateur|Le bois des quilles est lisse et chaud.
+narrateur|Une feuille colle à une quille.
+narrateur|Un nuage passe.
+narrateur|L'ombre bouge.
+narrateur|Le seau sent un peu la terre.
+narrateur|Une coccinelle marche sur une quille.
+narrateur|Elle s'envole.
+narrateur|La quille reste.
+papa|Tu as vu les fourmis, Chouchou ?
+enfant-m|Oui, papa. Elles marchent en file.
+narrateur|En ce moment, papa pose les quilles.
+narrateur|Elles font un petit bruit sourd.
+papa|Une règle. On attend.
+papa|Puis on fait rouler la balle.
+enfant-m|J'ai envie de rouler.
+papa|On attend. Je te la rappelle une fois.
+papa|C'est la règle.
+narrateur|Chouchou attend, la balle près du pied.
+narrateur|Puis il fait rouler la balle.
+narrateur|Une quille tombe.
+narrateur|Le bois claque.
+enfant-m|Elle est tombée.
 papa|Tu as suivi la règle.
-narrateur|Bérénice répète : on attend. Une règle simple. Papa la rappelle. Bérénice la suit. Plus tard, ils jouent au ballon souple. Papa dit une règle. Une règle : on se passe le ballon. Bérénice se souvient. Papa va la rappeler une fois. Bérénice attend. Puis elle passe le ballon. Même leçon, autre jeu. Une règle. On la rappelle. On la suit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Tu as attendu. Bravo, Chouchou.
+enfant-m|On attend. Puis on roule.
+papa|Oui. Une règle simple. On la rappelle.
+narrateur|Plus tard, le soleil a un peu baissé.
+narrateur|Papa sort un ballon souple.
+narrateur|Le ballon sent le caoutchouc tiède.
+papa|Une règle. On se passe le ballon.
+papa|On attend. Puis on passe.
+enfant-m|Je me souviens. On attend.
+papa|Oui. Je te la rappelle une fois.
+narrateur|Chouchou attend.
+narrateur|Puis il passe le ballon.
+papa|Tu as suivi la règle dite.
+papa|Au ballon, la même règle. Bravo.
+enfant-m|Une règle. On la rappelle.
+papa|Oui. Tu la suis. Tu as fait du bon travail.
+narrateur|Les fourmis sont encore dans l'allée.
+narrateur|Les quilles reposent près du seau.
+papa|Tu as attendu aux quilles, puis au ballon ?
+enfant-m|Oui. Deux jeux. Une règle.
+papa|Bravo, Chouchou. On la rappelle. On la suit.
+narrateur|Le ballon souple repose dans l'herbe.
+papa|Tu as attendu, chaque fois ?
+enfant-m|Oui. Quilles, puis ballon.
+papa|Une règle. Je la rappelle. Tu la suis.
+narrateur|Les fourmis avancent encore.
+narrateur|L'herbe pique un peu les chevilles.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1406,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Bérénice joue. Que suit-elle ?</t>
+          <t>Chouchou joue. Que suit-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,10 +1562,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Bérénice joue. Que suit-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Chouchou joue.
+narrateur|Que suit-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Bérénice a suivi la règle. Papa a su la rappeler. Plus tard, au ballon, pareil.</t>
+          <t>Chouchou a suivi la règle. Papa a su la rappeler. Plus tard, au ballon, pareil. Une règle, deux jeux. Tu as suivi ? Oui, papa. On attend. Bravo. On la rappelle, et on la suit. La balle repose près du seau.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,10 +1734,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Bérénice a suivi la règle. Papa a su la rappeler. Plus tard, au ballon, pareil.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Chouchou a suivi la règle.
+narrateur|Papa a su la rappeler.
+narrateur|Plus tard, au ballon, pareil.
+papa|Une règle, deux jeux. Tu as suivi ?
+enfant-m|Oui, papa. On attend.
+papa|Bravo. On la rappelle, et on la suit.
+narrateur|La balle repose près du seau.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,7 +1767,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Bérénice pose la balle. Papa lui verse de l'eau.</t>
+          <t>Chouchou pose la balle. Tu veux un peu d'eau ? Oui, papa. Papa verse de l'eau. L'eau est fraîche. Les fourmis sont encore là. Oui. Tout doux, l'allée. Chouchou essuie une main dans l'herbe. On range les quilles après ? Oui. Dans le seau.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,10 +1907,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Bérénice pose la balle. Papa lui verse de l'eau.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Chouchou pose la balle.
+papa|Tu veux un peu d'eau ?
+enfant-m|Oui, papa.
+narrateur|Papa verse de l'eau.
+narrateur|L'eau est fraîche.
+enfant-m|Les fourmis sont encore là.
+papa|Oui. Tout doux, l'allée.
+narrateur|Chouchou essuie une main dans l'herbe.
+papa|On range les quilles après ?
+enfant-m|Oui. Dans le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,7 +1943,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le seau reste près des quilles. J'ai attendu. Deux fois. Oui. Tu as suivi la règle. Bravo, Chouchou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,10 +2083,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le seau reste près des quilles.
+enfant-m|J'ai attendu. Deux fois.
+papa|Oui. Tu as suivi la règle.
+papa|Bravo, Chouchou.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2146,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-04.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une file de fourmis traverse l'allée. Les quilles en bois sentent le pin. Une balle ronde attend près du seau. L'herbe du jardin est un peu sèche. Un oiseau pique le sol, tout près. Le seau a un peu de terre au fond. Le bois des quilles est lisse et chaud. Une feuille colle à une quille. Un nuage passe. L'ombre bouge. Le seau sent un peu la terre. Une coccinelle marche sur une quille. Elle s'envole. La quille reste. Tu as vu les fourmis, Chouchou ? Oui, papa. Elles marchent en file. En ce moment, papa pose les quilles. Elles font un petit bruit sourd. Une règle. On attend. Puis on fait rouler la balle. J'ai envie de rouler. On attend. Je te la rappelle une fois. C'est la règle. Chouchou attend, la balle près du pied. Puis il fait rouler la balle. Une quille tombe. Le bois claque. Elle est tombée. Tu as suivi la règle. Tu as attendu. Bravo, Chouchou. On attend. Puis on roule. Oui. Une règle simple. On la rappelle. Plus tard, le soleil a un peu baissé. Papa sort un ballon souple. Le ballon sent le caoutchouc tiède. Une règle. On se passe le ballon. On attend. Puis on passe. Je me souviens. On attend. Oui. Je te la rappelle une fois. Chouchou attend. Puis il passe le ballon. Tu as suivi la règle dite. Au ballon, la même règle. Bravo. Une règle. On la rappelle. Oui. Tu la suis. Tu as fait du bon travail. Les fourmis sont encore dans l'allée. Les quilles reposent près du seau. Tu as attendu aux quilles, puis au ballon ? Oui. Deux jeux. Une règle. Bravo, Chouchou. On la rappelle. On la suit. Le ballon souple repose dans l'herbe. Tu as attendu, chaque fois ? Oui. Quilles, puis ballon. Une règle. Je la rappelle. Tu la suis. Les fourmis avancent encore. L'herbe pique un peu les chevilles.</t>
+          <t>Une file de fourmis traverse l'allée. Les quilles en bois sentent le pin. Une balle ronde attend près du seau. L'herbe du jardin est un peu sèche. Un oiseau pique le sol, tout près. Le seau a un peu de terre au fond. Le bois des quilles est lisse et chaud. Une feuille colle à une quille. Un nuage passe. L'ombre bouge. Le seau sent un peu la terre. Une coccinelle marche sur une quille. Elle s'envole. La quille reste. Tu as vu les fourmis, Chouchou ? Oui, papa. Elles marchent en file. En ce moment, papa pose les quilles. Elles font un petit bruit sourd. Une règle. On attend. Puis on fait rouler la balle. J'ai envie de rouler. On attend. Je te la rappelle une fois. C'est la règle. Chouchou attend, la balle près du pied. Puis il fait rouler la balle. Une quille tombe. Le bois claque. Elle est tombée. Tu as suivi la règle. Tu as attendu. Bravo, Chouchou. On attend. Puis on roule. Oui. Une règle simple. On la rappelle. Plus tard, le soleil a un peu baissé. Papa sort un ballon souple. Le ballon sent le caoutchouc tiède. Une règle. On se passe le ballon. On attend. Puis on passe. Je me souviens. On attend. Oui. Je te la rappelle une fois. Chouchou attend. Puis il passe le ballon. Tu as suivi la règle dite. Au ballon, la même règle. Bravo. Une règle. On la rappelle. Les fourmis sont encore dans l'allée. Les quilles reposent près du seau. Tu as attendu aux quilles, puis au ballon ? Oui. Deux jeux. Une règle. Bravo, Chouchou. On la rappelle. On la suit. Le ballon souple repose dans l'herbe. Tu as attendu, chaque fois ? Oui. Quilles, puis ballon. Une règle. Je la rappelle. Tu la suis. Les fourmis avancent encore. L'herbe pique un peu les chevilles.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bérénice joue dans le jardin. Papa est là. Il y a des quilles en bois. Papa dit &lt;emphasis level="moderate"&gt;une&lt;/emphasis&gt; règle. Une règle : on attend. Puis on fait rouler la balle. Bérénice écoute. Elle prend la balle trop vite. Papa va la rappeler une fois. Il dit : on attend. C'est la règle. Bérénice s'arrête. Elle attend. Puis elle fait rouler la balle. Une quille tombe. Bérénice sourit. Papa dit : tu as suivi la règle. Bérénice répète : on attend. Une règle simple. Papa la rappelle. Bérénice la suit. Plus tard, ils jouent au ballon souple. Papa dit une règle. Une règle : on se passe le ballon. Bérénice se souvient. Papa va la rappeler une fois. Bérénice attend. Puis elle passe le ballon. Même leçon, autre jeu. Une règle. On la rappelle. On la suit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une file de fourmis traverse l'allée. Les quilles en bois sentent le pin. Une balle ronde attend près du seau. L'herbe du jardin est un peu sèche. Un oiseau pique le sol, tout près. Le seau a un peu de terre au fond. Le bois des quilles est lisse et chaud. Une feuille colle à une quille. Un nuage passe. L'ombre bouge. Le seau sent un peu la terre. Une coccinelle marche sur une quille. Elle s'envole. La quille reste. Tu as vu les fourmis, Chouchou ? Oui, papa. Elles marchent en file. En ce moment, papa pose les quilles. Elles font un petit bruit sourd. Une règle. On attend. Puis on fait rouler la balle. J'ai envie de rouler. On attend. Je te la rappelle une fois. C'est la règle. Chouchou attend, la balle près du pied. Puis il fait rouler la balle. Une quille tombe. Le bois claque. Elle est tombée. Tu as suivi la règle. Tu as attendu. Bravo, Chouchou. On attend. Puis on roule. Oui. Une règle simple. On la rappelle. Plus tard, le soleil a un peu baissé. Papa sort un ballon souple. Le ballon sent le caoutchouc tiède. Une règle. On se passe le ballon. On attend. Puis on passe. Je me souviens. On attend. Oui. Je te la rappelle une fois. Chouchou attend. Puis il passe le ballon. Tu as suivi la règle dite. Au ballon, la même règle. Bravo. Une règle. On la rappelle. Les fourmis sont encore dans l'allée. Les quilles reposent près du seau. Tu as attendu aux quilles, puis au ballon ? Oui. Deux jeux. Une règle. Bravo, Chouchou. On la rappelle. On la suit. Le ballon souple repose dans l'herbe. Tu as attendu, chaque fois ? Oui. Quilles, puis ballon. Une règle. Je la rappelle. Tu la suis. Les fourmis avancent encore. L'herbe pique un peu les chevilles.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1368,7 +1368,6 @@
 papa|Tu as suivi la règle dite.
 papa|Au ballon, la même règle. Bravo.
 enfant-m|Une règle. On la rappelle.
-papa|Oui. Tu la suis. Tu as fait du bon travail.
 narrateur|Les fourmis sont encore dans l'allée.
 narrateur|Les quilles reposent près du seau.
 papa|Tu as attendu aux quilles, puis au ballon ?
@@ -1411,7 +1410,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bérénice joue. Que suit-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou joue. Que suit-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1595,7 +1594,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bérénice a suivi &lt;emphasis level="moderate"&gt;la&lt;/emphasis&gt; règle. Papa a su la rappeler. Plus tard, au ballon, pareil.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a suivi la règle. Papa a su la rappeler. Plus tard, au ballon, pareil. Une règle, deux jeux. Tu as suivi ? Oui, papa. On attend. Bravo. On la rappelle, et on la suit. La balle repose près du seau.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1772,7 +1771,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bérénice pose &lt;emphasis level="moderate"&gt;la&lt;/emphasis&gt; balle. Papa lui verse de l'eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou pose la balle. Tu veux un peu d'eau ? Oui, papa. Papa verse de l'eau. L'eau est fraîche. Les fourmis sont encore là. Oui. Tout doux, l'allée. Chouchou essuie une main dans l'herbe. On range les quilles après ? Oui. Dans le seau.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1943,12 +1942,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le seau reste près des quilles. J'ai attendu. Deux fois. Oui. Tu as suivi la règle. Bravo, Chouchou. L'histoire est finie.</t>
+          <t>Le seau reste près des quilles. J'ai attendu. Deux fois. Oui. Tu as suivi la règle. Bravo, Chouchou.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le seau reste près des quilles. J'ai attendu. Deux fois. Oui. Tu as suivi la règle. Bravo, Chouchou.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2086,8 +2085,7 @@
           <t>narrateur|Le seau reste près des quilles.
 enfant-m|J'ai attendu. Deux fois.
 papa|Oui. Tu as suivi la règle.
-papa|Bravo, Chouchou.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Chouchou.</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2153,6 +2151,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-04.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin, allée des fourmis, quilles en bois puis ballon souple</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bérénice, papa</t>
+          <t>Chouchou, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-04.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-04.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les quilles de Chouchou, puis le ballon</t>
+          <t>Les quilles dans le romarin</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin, allée des fourmis, quilles en bois puis ballon souple</t>
+          <t>jardin de montagne, pins, gravier, après-midi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chouchou, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Au jardin, Chouchou suit une règle aux quilles, puis au ballon. Papa rappelle une fois, chaque fois.</t>
+          <t>Nina veut faire tomber les quilles blondes. Elle lance trop tôt, une quille part dans le romarin. Ils attendent un peu. Toc. Plus tard, le ballon rouge ne part pas dans le thym.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une file de fourmis traverse l'allée. Les quilles en bois sentent le pin. Une balle ronde attend près du seau. L'herbe du jardin est un peu sèche. Un oiseau pique le sol, tout près. Le seau a un peu de terre au fond. Le bois des quilles est lisse et chaud. Une feuille colle à une quille. Un nuage passe. L'ombre bouge. Le seau sent un peu la terre. Une coccinelle marche sur une quille. Elle s'envole. La quille reste. Tu as vu les fourmis, Chouchou ? Oui, papa. Elles marchent en file. En ce moment, papa pose les quilles. Elles font un petit bruit sourd. Une règle. On attend. Puis on fait rouler la balle. J'ai envie de rouler. On attend. Je te la rappelle une fois. C'est la règle. Chouchou attend, la balle près du pied. Puis il fait rouler la balle. Une quille tombe. Le bois claque. Elle est tombée. Tu as suivi la règle. Tu as attendu. Bravo, Chouchou. On attend. Puis on roule. Oui. Une règle simple. On la rappelle. Plus tard, le soleil a un peu baissé. Papa sort un ballon souple. Le ballon sent le caoutchouc tiède. Une règle. On se passe le ballon. On attend. Puis on passe. Je me souviens. On attend. Oui. Je te la rappelle une fois. Chouchou attend. Puis il passe le ballon. Tu as suivi la règle dite. Au ballon, la même règle. Bravo. Une règle. On la rappelle. Les fourmis sont encore dans l'allée. Les quilles reposent près du seau. Tu as attendu aux quilles, puis au ballon ? Oui. Deux jeux. Une règle. Bravo, Chouchou. On la rappelle. On la suit. Le ballon souple repose dans l'herbe. Tu as attendu, chaque fois ? Oui. Quilles, puis ballon. Une règle. Je la rappelle. Tu la suis. Les fourmis avancent encore. L'herbe pique un peu les chevilles.</t>
+          <t>Les aiguilles de pin tapissent le gravier. Ça sent la résine chaude. Le romarin fait un nuage gris, tout bas. La montagne est proche, toute bleue. Un lézard part sous une pierre. Les quilles de bois attendent en tas. Nina, tu vois les quilles ? Oui, papa. Elles sont blondes. Papa pose déjà trois quilles. La quatrième penche encore. En ce moment, Nina prend la balle. Je veux les faire tomber. Toutes. J'ai pas fini le rang. Nina lance quand même. La balle part trop vite. Elle tape le gravier, à côté. Une quille roule dans le romarin. Les autres s'éparpillent. Oh. Elle est partie. Le jeu s'est arrêté. On attend un peu ? Nina s'arrête au bord du gravier. Les aiguilles collent à ses chaussures. Ça sent le pin, tout fort. Je cherche la quille ? Oui. Dans le romarin, tout doux. Les feuilles piquent un peu les doigts. Nina trouve le bois lisse. Je l'ai. On les remet, une par une. Papa pose la dernière quille. Le rang est droit, cette fois. Tu attends que je sois prêt ? Oui. On attend un peu. Nina tient la balle contre le ventre. Elle est ronde, un peu rêche. Le lézard revient sur la pierre. Le romarin ne bouge plus.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Une file de fourmis traverse l'allée. Les quilles en bois sentent le pin. Une balle ronde attend près du seau. L'herbe du jardin est un peu sèche. Un oiseau pique le sol, tout près. Le seau a un peu de terre au fond. Le bois des quilles est lisse et chaud. Une feuille colle à une quille. Un nuage passe. L'ombre bouge. Le seau sent un peu la terre. Une coccinelle marche sur une quille. Elle s'envole. La quille reste. Tu as vu les fourmis, Chouchou ? Oui, papa. Elles marchent en file. En ce moment, papa pose les quilles. Elles font un petit bruit sourd. Une règle. On attend. Puis on fait rouler la balle. J'ai envie de rouler. On attend. Je te la rappelle une fois. C'est la règle. Chouchou attend, la balle près du pied. Puis il fait rouler la balle. Une quille tombe. Le bois claque. Elle est tombée. Tu as suivi la règle. Tu as attendu. Bravo, Chouchou. On attend. Puis on roule. Oui. Une règle simple. On la rappelle. Plus tard, le soleil a un peu baissé. Papa sort un ballon souple. Le ballon sent le caoutchouc tiède. Une règle. On se passe le ballon. On attend. Puis on passe. Je me souviens. On attend. Oui. Je te la rappelle une fois. Chouchou attend. Puis il passe le ballon. Tu as suivi la règle dite. Au ballon, la même règle. Bravo. Une règle. On la rappelle. Les fourmis sont encore dans l'allée. Les quilles reposent près du seau. Tu as attendu aux quilles, puis au ballon ? Oui. Deux jeux. Une règle. Bravo, Chouchou. On la rappelle. On la suit. Le ballon souple repose dans l'herbe. Tu as attendu, chaque fois ? Oui. Quilles, puis ballon. Une règle. Je la rappelle. Tu la suis. Les fourmis avancent encore. L'herbe pique un peu les chevilles.</t>
+          <t>Les aiguilles de pin tapissent le gravier. Ça sent la résine chaude. Le romarin fait un nuage gris, tout bas. La montagne est proche, toute bleue. Un lézard part sous une pierre. Les quilles de bois attendent en tas. Nina, tu vois les quilles ? Oui, papa. Elles sont blondes. Papa pose déjà trois quilles. La quatrième penche encore. En ce moment, Nina prend la balle. Je veux les faire tomber. Toutes. J'ai pas fini le rang. Nina lance quand même. La balle part trop vite. Elle tape le gravier, à côté. Une quille roule dans le romarin. Les autres s'éparpillent. Oh. Elle est partie. Le jeu s'est arrêté. On attend un peu ? Nina s'arrête au bord du gravier. Les aiguilles collent à ses chaussures. Ça sent le pin, tout fort. Je cherche la quille ? Oui. Dans le romarin, tout doux. Les feuilles piquent un peu les doigts. Nina trouve le bois lisse. Je l'ai. On les remet, une par une. Papa pose la dernière quille. Le rang est droit, cette fois. Tu attends que je sois prêt ? Oui. On attend un peu. Nina tient la balle contre le ventre. Elle est ronde, un peu rêche. Le lézard revient sur la pierre. Le romarin ne bouge plus.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,61 +1324,49 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une file de fourmis traverse l'allée.
-narrateur|Les quilles en bois sentent le pin.
-narrateur|Une balle ronde attend près du seau.
-narrateur|L'herbe du jardin est un peu sèche.
-narrateur|Un oiseau pique le sol, tout près.
-narrateur|Le seau a un peu de terre au fond.
-narrateur|Le bois des quilles est lisse et chaud.
-narrateur|Une feuille colle à une quille.
-narrateur|Un nuage passe.
-narrateur|L'ombre bouge.
-narrateur|Le seau sent un peu la terre.
-narrateur|Une coccinelle marche sur une quille.
-narrateur|Elle s'envole.
-narrateur|La quille reste.
-papa|Tu as vu les fourmis, Chouchou ?
-enfant-m|Oui, papa. Elles marchent en file.
-narrateur|En ce moment, papa pose les quilles.
-narrateur|Elles font un petit bruit sourd.
-papa|Une règle. On attend.
-papa|Puis on fait rouler la balle.
-enfant-m|J'ai envie de rouler.
-papa|On attend. Je te la rappelle une fois.
-papa|C'est la règle.
-narrateur|Chouchou attend, la balle près du pied.
-narrateur|Puis il fait rouler la balle.
-narrateur|Une quille tombe.
-narrateur|Le bois claque.
-enfant-m|Elle est tombée.
-papa|Tu as suivi la règle.
-papa|Tu as attendu. Bravo, Chouchou.
-enfant-m|On attend. Puis on roule.
-papa|Oui. Une règle simple. On la rappelle.
-narrateur|Plus tard, le soleil a un peu baissé.
-narrateur|Papa sort un ballon souple.
-narrateur|Le ballon sent le caoutchouc tiède.
-papa|Une règle. On se passe le ballon.
-papa|On attend. Puis on passe.
-enfant-m|Je me souviens. On attend.
-papa|Oui. Je te la rappelle une fois.
-narrateur|Chouchou attend.
-narrateur|Puis il passe le ballon.
-papa|Tu as suivi la règle dite.
-papa|Au ballon, la même règle. Bravo.
-enfant-m|Une règle. On la rappelle.
-narrateur|Les fourmis sont encore dans l'allée.
-narrateur|Les quilles reposent près du seau.
-papa|Tu as attendu aux quilles, puis au ballon ?
-enfant-m|Oui. Deux jeux. Une règle.
-papa|Bravo, Chouchou. On la rappelle. On la suit.
-narrateur|Le ballon souple repose dans l'herbe.
-papa|Tu as attendu, chaque fois ?
-enfant-m|Oui. Quilles, puis ballon.
-papa|Une règle. Je la rappelle. Tu la suis.
-narrateur|Les fourmis avancent encore.
-narrateur|L'herbe pique un peu les chevilles.</t>
+          <t>narrateur|Les aiguilles de pin tapissent le gravier.
+narrateur|Ça sent la résine chaude.
+narrateur|Le romarin fait un nuage gris, tout bas.
+narrateur|La montagne est proche, toute bleue.
+narrateur|Un lézard part sous une pierre.
+narrateur|Les quilles de bois attendent en tas.
+papa|Nina, tu vois les quilles ?
+enfant-f|Oui, papa.
+enfant-f|Elles sont blondes.
+narrateur|Papa pose déjà trois quilles.
+narrateur|La quatrième penche encore.
+narrateur|En ce moment, Nina prend la balle.
+enfant-f|Je veux les faire tomber.
+enfant-f|Toutes.
+papa|J'ai pas fini le rang.
+narrateur|Nina lance quand même.
+narrateur|La balle part trop vite.
+narrateur|Elle tape le gravier, à côté.
+narrateur|Une quille roule dans le romarin.
+narrateur|Les autres s'éparpillent.
+enfant-f|Oh.
+enfant-f|Elle est partie.
+papa|Le jeu s'est arrêté.
+papa|On attend un peu ?
+narrateur|Nina s'arrête au bord du gravier.
+narrateur|Les aiguilles collent à ses chaussures.
+narrateur|Ça sent le pin, tout fort.
+enfant-f|Je cherche la quille ?
+papa|Oui.
+papa|Dans le romarin, tout doux.
+narrateur|Les feuilles piquent un peu les doigts.
+narrateur|Nina trouve le bois lisse.
+enfant-f|Je l'ai.
+papa|On les remet, une par une.
+narrateur|Papa pose la dernière quille.
+narrateur|Le rang est droit, cette fois.
+papa|Tu attends que je sois prêt ?
+enfant-f|Oui.
+papa|On attend un peu.
+narrateur|Nina tient la balle contre le ventre.
+narrateur|Elle est ronde, un peu rêche.
+narrateur|Le lézard revient sur la pierre.
+narrateur|Le romarin ne bouge plus.</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1393,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Chouchou joue. Que suit-il ?</t>
+          <t>Nina veut lancer. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Chouchou joue. Que suit-il ?</t>
+          <t>Nina veut lancer. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1420,12 +1408,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>la règle</t>
+          <t>attendre</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>la règle | une règle | attendre | on attend</t>
+          <t>attendre | on attend | un peu | son tour | elle attend | il attend | attendre un peu | on attend un peu | à son tour</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1440,7 +1428,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Papa la dit encore. C'est quoi ?</t>
+          <t>Elle reste un peu. Que fait Nina d'abord ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1482,14 +1470,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1561,8 +1549,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Chouchou joue.
-narrateur|Que suit-il ?</t>
+          <t>narrateur|Nina veut lancer.
+narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1577,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a suivi la règle. Papa a su la rappeler. Plus tard, au ballon, pareil. Une règle, deux jeux. Tu as suivi ? Oui, papa. On attend. Bravo. On la rappelle, et on la suit. La balle repose près du seau.</t>
+          <t>Nina reste encore un peu. Le rang est prêt. Tu peux lancer. J'y vais. Elle fait rouler la balle. La balle avance sur le gravier. Toc. Deux quilles tombent, tout net. Elles sont tombées ! Oui. Le rang a tenu, d'abord. Le bois sent encore la résine. Nina ramasse les quilles blondes. Encore une fois ? Encore. On attend un peu. Papa remet le rang. Nina compte, sans lancer. Un. Deux. Maintenant. Toc, encore. Merci, Nina. Le bois fait un beau bruit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a suivi la règle. Papa a su la rappeler. Plus tard, au ballon, pareil. Une règle, deux jeux. Tu as suivi ? Oui, papa. On attend. Bravo. On la rappelle, et on la suit. La balle repose près du seau.</t>
+          <t>Nina reste encore un peu. Le rang est prêt. Tu peux lancer. J'y vais. Elle fait rouler la balle. La balle avance sur le gravier. Toc. Deux quilles tombent, tout net. Elles sont tombées ! Oui. Le rang a tenu, d'abord. Le bois sent encore la résine. Nina ramasse les quilles blondes. Encore une fois ? Encore. On attend un peu. Papa remet le rang. Nina compte, sans lancer. Un. Deux. Maintenant. Toc, encore. Merci, Nina. Le bois fait un beau bruit.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1657,7 +1645,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1733,13 +1721,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Chouchou a suivi la règle.
-narrateur|Papa a su la rappeler.
-narrateur|Plus tard, au ballon, pareil.
-papa|Une règle, deux jeux. Tu as suivi ?
-enfant-m|Oui, papa. On attend.
-papa|Bravo. On la rappelle, et on la suit.
-narrateur|La balle repose près du seau.</t>
+          <t>narrateur|Nina reste encore un peu.
+papa|Le rang est prêt.
+papa|Tu peux lancer.
+enfant-f|J'y vais.
+narrateur|Elle fait rouler la balle.
+narrateur|La balle avance sur le gravier.
+narrateur|Toc.
+narrateur|Deux quilles tombent, tout net.
+enfant-f|Elles sont tombées !
+papa|Oui.
+papa|Le rang a tenu, d'abord.
+narrateur|Le bois sent encore la résine.
+narrateur|Nina ramasse les quilles blondes.
+papa|Encore une fois ?
+enfant-f|Encore.
+papa|On attend un peu.
+narrateur|Papa remet le rang.
+narrateur|Nina compte, sans lancer.
+narrateur|Un.
+narrateur|Deux.
+papa|Maintenant.
+narrateur|Toc, encore.
+papa|Merci, Nina.
+enfant-f|Le bois fait un beau bruit.</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1771,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Chouchou pose la balle. Tu veux un peu d'eau ? Oui, papa. Papa verse de l'eau. L'eau est fraîche. Les fourmis sont encore là. Oui. Tout doux, l'allée. Chouchou essuie une main dans l'herbe. On range les quilles après ? Oui. Dans le seau.</t>
+          <t>Plus tard, le ballon ? Oui, le rouge. Le ballon rouge attend près du thym. Le thym sent le citron, un peu. Papa ouvre les mains. Je le prends. Attends un peu. Nina s'arrête. Elle ne lance pas tout de suite. Mes mains sont ouvertes. Tu es prête ? Oui, papa. Elle envoie le ballon, tout doux. Il ne part pas dans le thym. Il arrive dans les mains de papa. Tu l'as ! Oui. Comme les quilles. La montagne est plus bleue, maintenant. Un oiseau passe au-dessus des pins. On rejoue aux quilles ? Un dernier rang. Quand elles sont droites.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Chouchou pose la balle. Tu veux un peu d'eau ? Oui, papa. Papa verse de l'eau. L'eau est fraîche. Les fourmis sont encore là. Oui. Tout doux, l'allée. Chouchou essuie une main dans l'herbe. On range les quilles après ? Oui. Dans le seau.</t>
+          <t>Plus tard, le ballon ? Oui, le rouge. Le ballon rouge attend près du thym. Le thym sent le citron, un peu. Papa ouvre les mains. Je le prends. Attends un peu. Nina s'arrête. Elle ne lance pas tout de suite. Mes mains sont ouvertes. Tu es prête ? Oui, papa. Elle envoie le ballon, tout doux. Il ne part pas dans le thym. Il arrive dans les mains de papa. Tu l'as ! Oui. Comme les quilles. La montagne est plus bleue, maintenant. Un oiseau passe au-dessus des pins. On rejoue aux quilles ? Un dernier rang. Quand elles sont droites.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1834,7 +1839,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1906,16 +1911,29 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Chouchou pose la balle.
-papa|Tu veux un peu d'eau ?
-enfant-m|Oui, papa.
-narrateur|Papa verse de l'eau.
-narrateur|L'eau est fraîche.
-enfant-m|Les fourmis sont encore là.
-papa|Oui. Tout doux, l'allée.
-narrateur|Chouchou essuie une main dans l'herbe.
-papa|On range les quilles après ?
-enfant-m|Oui. Dans le seau.</t>
+          <t>papa|Plus tard, le ballon ?
+enfant-f|Oui, le rouge.
+narrateur|Le ballon rouge attend près du thym.
+narrateur|Le thym sent le citron, un peu.
+narrateur|Papa ouvre les mains.
+enfant-f|Je le prends.
+papa|Attends un peu.
+narrateur|Nina s'arrête.
+narrateur|Elle ne lance pas tout de suite.
+papa|Mes mains sont ouvertes.
+papa|Tu es prête ?
+enfant-f|Oui, papa.
+narrateur|Elle envoie le ballon, tout doux.
+narrateur|Il ne part pas dans le thym.
+narrateur|Il arrive dans les mains de papa.
+enfant-f|Tu l'as !
+papa|Oui.
+papa|Comme les quilles.
+narrateur|La montagne est plus bleue, maintenant.
+narrateur|Un oiseau passe au-dessus des pins.
+enfant-f|On rejoue aux quilles ?
+papa|Un dernier rang.
+papa|Quand elles sont droites.</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le seau reste près des quilles. J'ai attendu. Deux fois. Oui. Tu as suivi la règle. Bravo, Chouchou.</t>
+          <t>Les quilles sont blondes au soleil. Et toi, tu as attendu. Bravo, Nina. Le romarin sent encore, tout bas. Le bois tiède tient dans ses mains.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le seau reste près des quilles. J'ai attendu. Deux fois. Oui. Tu as suivi la règle. Bravo, Chouchou.</t>
+          <t>Les quilles sont blondes au soleil. Et toi, tu as attendu. Bravo, Nina. Le romarin sent encore, tout bas. Le bois tiède tient dans ses mains.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2010,7 +2028,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2082,10 +2100,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Le seau reste près des quilles.
-enfant-m|J'ai attendu. Deux fois.
-papa|Oui. Tu as suivi la règle.
-papa|Bravo, Chouchou.</t>
+          <t>enfant-f|Les quilles sont blondes au soleil.
+papa|Et toi, tu as attendu.
+papa|Bravo, Nina.
+narrateur|Le romarin sent encore, tout bas.
+narrateur|Le bois tiède tient dans ses mains.</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2156,6 +2175,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
